--- a/Results/tables/06_correlations.xlsx
+++ b/Results/tables/06_correlations.xlsx
@@ -1,36 +1,132 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sentiment_x_sentiment" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_x_sentiment" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_x_returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="sentiment_x_sentiment" sheetId="1" r:id="rId1"/>
+    <sheet name="returns_x_sentiment" sheetId="2" r:id="rId2"/>
+    <sheet name="returns_x_returns" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="31">
+  <si>
+    <t>S_All</t>
+  </si>
+  <si>
+    <t>S_Monetary</t>
+  </si>
+  <si>
+    <t>S_Fiscal</t>
+  </si>
+  <si>
+    <t>S_External</t>
+  </si>
+  <si>
+    <t>S_Energy</t>
+  </si>
+  <si>
+    <t>r_Market</t>
+  </si>
+  <si>
+    <t>r_Automobile_Assembler</t>
+  </si>
+  <si>
+    <t>r_Automobile_Parts_Accessories</t>
+  </si>
+  <si>
+    <t>r_Cable_Electrical_Goods</t>
+  </si>
+  <si>
+    <t>r_Cement</t>
+  </si>
+  <si>
+    <t>r_Chemical</t>
+  </si>
+  <si>
+    <t>r_Commercial_Banks</t>
+  </si>
+  <si>
+    <t>r_Engineering</t>
+  </si>
+  <si>
+    <t>r_Fertilizer</t>
+  </si>
+  <si>
+    <t>r_Food_Personal_Care_Products</t>
+  </si>
+  <si>
+    <t>r_Glass_Ceramics</t>
+  </si>
+  <si>
+    <t>r_Insurance</t>
+  </si>
+  <si>
+    <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
+  </si>
+  <si>
+    <t>r_Leather_Tanneries</t>
+  </si>
+  <si>
+    <t>r_Modarabas</t>
+  </si>
+  <si>
+    <t>r_Oil_Gas_Exploration_Companies</t>
+  </si>
+  <si>
+    <t>r_Oil_Gas_Marketing_Companies</t>
+  </si>
+  <si>
+    <t>r_Paper_Board_Packaging</t>
+  </si>
+  <si>
+    <t>r_Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>r_Power_Generation_Distribution</t>
+  </si>
+  <si>
+    <t>r_Refinery</t>
+  </si>
+  <si>
+    <t>r_Sugar_Allied_Industries</t>
+  </si>
+  <si>
+    <t>r_Technology_Communication</t>
+  </si>
+  <si>
+    <t>r_Textile_Composite</t>
+  </si>
+  <si>
+    <t>r_Textile_Spinning</t>
+  </si>
+  <si>
+    <t>r_Transport</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,80 +145,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -410,3121 +439,2923 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>S_All</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>S_Monetary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>S_Fiscal</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>S_External</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>S_Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S_All</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>0.676</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.292</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.637</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.26</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S_Monetary</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>0.676</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.21</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.299</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.229</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S_Fiscal</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>0.292</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.21</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.311</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.292</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S_External</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>0.637</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.299</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.311</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.204</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S_Energy</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>0.26</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.229</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.292</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.204</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>S_All</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>S_Monetary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>S_Fiscal</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>S_External</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>S_Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>r_Market</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.074</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.029</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.09</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>r_Automobile_Assembler</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>0.079</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.079</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.039</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.073</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.067</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>r_Automobile_Parts_Accessories</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>0.058</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.058</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.015</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.062</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.082</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>r_Cable_Electrical_Goods</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>0.061</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.047</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.034</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.056</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.062</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>r_Cement</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0.075</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.02</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.056</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.073</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>r_Chemical</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.065</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.041</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.066</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.09</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>r_Commercial_Banks</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0.059</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.061</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.016</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.042</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.089</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>r_Engineering</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0.061</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.066</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.019</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.053</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.06900000000000001</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>r_Fertilizer</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>0.091</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.045</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.048</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.098</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>r_Food_Personal_Care_Products</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
         <v>0.073</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>0.061</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.025</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.063</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.08699999999999999</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>r_Glass_Ceramics</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
         <v>0.055</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.045</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.038</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.064</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.079</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>r_Insurance</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
         <v>0.044</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.038</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.013</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.037</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.045</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.08599999999999999</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.008999999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.052</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.08500000000000001</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>r_Leather_Tanneries</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
         <v>0.064</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.05</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.015</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.044</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.063</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>r_Modarabas</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
         <v>0.038</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.036</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-0.008</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.016</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.038</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Exploration_Companies</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
         <v>0.07199999999999999</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.05</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.051</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.048</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.141</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Marketing_Companies</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
         <v>0.067</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.041</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.038</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.04</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.095</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>r_Paper_Board_Packaging</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
         <v>0.05</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.035</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.057</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.053</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>r_Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
         <v>0.094</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.099</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.032</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.068</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.05</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>r_Power_Generation_Distribution</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
         <v>0.043</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.031</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>-0.005</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.033</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.032</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>r_Refinery</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
         <v>0.028</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.042</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.028</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.018</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.076</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>r_Sugar_Allied_Industries</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
         <v>0.031</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.026</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.011</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.003</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.05</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>r_Technology_Communication</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
         <v>0.059</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.041</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.029</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.052</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.08599999999999999</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>r_Textile_Composite</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
         <v>0.067</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.049</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.025</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.053</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.059</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>r_Textile_Spinning</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
         <v>0.1</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>0.079</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.04</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.091</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.066</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>r_Transport</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>0.059</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.011</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.068</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0.042</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>r_Market</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>r_Automobile_Assembler</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>r_Automobile_Parts_Accessories</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>r_Cable_Electrical_Goods</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>r_Cement</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>r_Chemical</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>r_Commercial_Banks</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>r_Engineering</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>r_Fertilizer</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>r_Food_Personal_Care_Products</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>r_Glass_Ceramics</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>r_Insurance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>r_Leather_Tanneries</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>r_Modarabas</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Exploration_Companies</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Marketing_Companies</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>r_Paper_Board_Packaging</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>r_Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>r_Power_Generation_Distribution</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>r_Refinery</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>r_Sugar_Allied_Industries</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>r_Technology_Communication</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>r_Textile_Composite</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>r_Textile_Spinning</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>r_Transport</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>r_Market</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:27">
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.803</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.799</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.748</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.833</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.862</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.756</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.855</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.742</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.888</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.797</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.678</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.854</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.485</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>0.446</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>0.668</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>0.824</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>0.8129999999999999</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>0.768</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>0.708</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>0.746</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2">
         <v>0.651</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2">
         <v>0.874</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2">
         <v>0.782</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>0.748</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2">
         <v>0.678</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>r_Automobile_Assembler</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:27">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>0.803</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.696</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.579</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.676</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.6929999999999999</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.571</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.703</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.595</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.71</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.646</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.506</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.65</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.386</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>0.335</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>0.531</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>0.662</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>0.654</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>0.646</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>0.54</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>0.615</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3">
         <v>0.511</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3">
         <v>0.713</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3">
         <v>0.57</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>0.5580000000000001</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3">
         <v>0.546</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>r_Automobile_Parts_Accessories</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:27">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>0.799</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.696</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.584</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.661</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.699</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.601</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.595</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.716</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.634</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.517</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.65</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.413</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>0.315</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>0.552</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>0.644</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4">
         <v>0.654</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>0.67</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>0.554</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>0.613</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4">
         <v>0.499</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4">
         <v>0.6879999999999999</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4">
         <v>0.614</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4">
         <v>0.527</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4">
         <v>0.549</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>r_Cable_Electrical_Goods</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:27">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>0.748</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.579</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.584</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.625</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.651</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.549</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.662</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.519</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.666</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.61</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.484</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.623</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.37</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>0.309</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>0.466</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>0.599</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5">
         <v>0.606</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>0.576</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>0.502</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>0.556</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5">
         <v>0.477</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5">
         <v>0.655</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5">
         <v>0.5620000000000001</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5">
         <v>0.539</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5">
         <v>0.516</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>r_Cement</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:27">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0.833</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.676</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.661</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.625</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.702</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.616</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.76</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.626</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.72</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.678</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.519</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.663</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.413</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>0.317</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>0.57</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>0.671</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6">
         <v>0.6820000000000001</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>0.652</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6">
         <v>0.5610000000000001</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6">
         <v>0.627</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6">
         <v>0.495</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6">
         <v>0.698</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6">
         <v>0.647</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z6">
         <v>0.542</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6">
         <v>0.526</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>r_Chemical</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:27">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0.862</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.6929999999999999</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.699</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.651</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.702</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.609</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.733</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.632</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.766</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.722</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.538</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.713</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.415</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>0.34</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>0.571</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>0.713</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7">
         <v>0.71</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>0.67</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>0.599</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>0.625</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7">
         <v>0.552</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7">
         <v>0.749</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7">
         <v>0.656</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7">
         <v>0.613</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7">
         <v>0.587</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>r_Commercial_Banks</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:27">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0.756</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.571</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.601</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.549</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.616</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.609</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>0.621</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.646</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.645</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0.532</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>0.52</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>0.637</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>0.367</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>0.315</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>0.555</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8">
         <v>0.62</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8">
         <v>0.596</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8">
         <v>0.577</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8">
         <v>0.549</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>0.525</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W8">
         <v>0.444</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X8">
         <v>0.614</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y8">
         <v>0.546</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z8">
         <v>0.503</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8">
         <v>0.51</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>r_Engineering</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:27">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0.855</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.703</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.6879999999999999</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.662</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.76</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.733</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.621</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>0.606</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.751</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.6919999999999999</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.5570000000000001</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>0.695</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.419</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>0.345</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>0.539</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9">
         <v>0.6870000000000001</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9">
         <v>0.7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9">
         <v>0.645</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9">
         <v>0.5659999999999999</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9">
         <v>0.639</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W9">
         <v>0.512</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9">
         <v>0.743</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9">
         <v>0.663</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9">
         <v>0.592</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9">
         <v>0.582</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>r_Fertilizer</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:27">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>0.742</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.595</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.595</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.519</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.626</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.632</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.646</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>0.606</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.65</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0.57</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.506</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>0.617</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>0.375</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>0.309</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>0.574</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>0.616</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10">
         <v>0.605</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10">
         <v>0.585</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10">
         <v>0.538</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10">
         <v>0.516</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10">
         <v>0.457</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10">
         <v>0.607</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10">
         <v>0.546</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10">
         <v>0.52</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10">
         <v>0.503</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>r_Food_Personal_Care_Products</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:27">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
         <v>0.888</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>0.71</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.716</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.666</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.72</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.766</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.645</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>0.751</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>0.65</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0.707</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.5679999999999999</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>0.748</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>0.43</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>0.345</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>0.571</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11">
         <v>0.74</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11">
         <v>0.72</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>0.679</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11">
         <v>0.603</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11">
         <v>0.665</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W11">
         <v>0.5620000000000001</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X11">
         <v>0.784</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11">
         <v>0.676</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>0.638</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11">
         <v>0.601</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>r_Glass_Ceramics</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:27">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
         <v>0.797</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.646</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.634</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.61</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.678</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.722</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.532</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.6919999999999999</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>0.57</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.707</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>0.489</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>0.651</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>0.352</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>0.321</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>0.512</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>0.655</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12">
         <v>0.676</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>0.616</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12">
         <v>0.547</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12">
         <v>0.585</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W12">
         <v>0.51</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12">
         <v>0.707</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12">
         <v>0.631</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>0.571</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12">
         <v>0.531</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>r_Insurance</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:27">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
         <v>0.678</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.506</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.517</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.484</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.519</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.538</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.52</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>0.5570000000000001</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>0.506</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>0.5679999999999999</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>0.489</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>0.57</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>0.358</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>0.284</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>0.437</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13">
         <v>0.525</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13">
         <v>0.53</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13">
         <v>0.463</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13">
         <v>0.431</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13">
         <v>0.482</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W13">
         <v>0.433</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X13">
         <v>0.5580000000000001</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13">
         <v>0.489</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z13">
         <v>0.487</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13">
         <v>0.452</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:27">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
         <v>0.854</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.65</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.65</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.623</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.663</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.713</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>0.637</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.695</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>0.617</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>0.748</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>0.651</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>0.57</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>0.378</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>0.389</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>0.54</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14">
         <v>0.672</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14">
         <v>0.672</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14">
         <v>0.618</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14">
         <v>0.578</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14">
         <v>0.63</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W14">
         <v>0.53</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X14">
         <v>0.763</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14">
         <v>0.638</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z14">
         <v>0.633</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14">
         <v>0.578</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>r_Leather_Tanneries</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:27">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
         <v>0.485</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.386</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.413</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.37</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.413</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.415</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>0.367</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.419</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>0.375</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>0.43</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>0.352</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>0.358</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.378</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>1</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>0.168</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>0.317</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>0.395</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15">
         <v>0.413</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15">
         <v>0.379</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15">
         <v>0.332</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15">
         <v>0.353</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W15">
         <v>0.278</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X15">
         <v>0.415</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15">
         <v>0.363</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z15">
         <v>0.315</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15">
         <v>0.32</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>r_Modarabas</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:27">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
         <v>0.446</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.335</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.315</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.309</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.317</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>0.34</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>0.315</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>0.345</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.309</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>0.345</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>0.321</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>0.284</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>0.389</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>0.168</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>0.246</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16">
         <v>0.322</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16">
         <v>0.302</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16">
         <v>0.301</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U16">
         <v>0.298</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16">
         <v>0.301</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W16">
         <v>0.27</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X16">
         <v>0.37</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16">
         <v>0.316</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z16">
         <v>0.32</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16">
         <v>0.278</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Exploration_Companies</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:27">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
         <v>0.668</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.531</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.552</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.466</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.57</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>0.571</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.555</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>0.539</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.574</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>0.571</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>0.512</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>0.437</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>0.54</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>0.317</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>0.246</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17">
         <v>0.6840000000000001</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17">
         <v>0.526</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17">
         <v>0.551</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17">
         <v>0.522</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17">
         <v>0.552</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W17">
         <v>0.421</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X17">
         <v>0.549</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17">
         <v>0.478</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z17">
         <v>0.421</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17">
         <v>0.463</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Marketing_Companies</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:27">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
         <v>0.824</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.662</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.644</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.599</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.671</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>0.713</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>0.62</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>0.6870000000000001</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>0.616</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>0.74</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>0.655</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>0.525</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>0.672</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>0.395</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>0.322</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>0.6840000000000001</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18">
         <v>0.656</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18">
         <v>0.655</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18">
         <v>0.603</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18">
         <v>0.673</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W18">
         <v>0.515</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X18">
         <v>0.717</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18">
         <v>0.614</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18">
         <v>0.5620000000000001</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18">
         <v>0.574</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>r_Paper_Board_Packaging</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:27">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
         <v>0.8129999999999999</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.654</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.654</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.606</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.6820000000000001</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>0.71</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>0.596</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>0.7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.605</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>0.72</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>0.676</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>0.53</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>0.672</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>0.413</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>0.302</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>0.526</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19">
         <v>0.656</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19">
         <v>0.64</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U19">
         <v>0.5649999999999999</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19">
         <v>0.569</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W19">
         <v>0.504</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X19">
         <v>0.698</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19">
         <v>0.646</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z19">
         <v>0.57</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19">
         <v>0.551</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>r_Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:27">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
         <v>0.768</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.646</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.67</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.576</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.652</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>0.67</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>0.577</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>0.645</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>0.585</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>0.679</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>0.616</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>0.463</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>0.618</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>0.379</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>0.301</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>0.551</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20">
         <v>0.655</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20">
         <v>0.64</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U20">
         <v>0.542</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20">
         <v>0.574</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W20">
         <v>0.455</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X20">
         <v>0.649</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20">
         <v>0.573</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z20">
         <v>0.512</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20">
         <v>0.528</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>r_Power_Generation_Distribution</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:27">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
         <v>0.708</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.54</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.554</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.502</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.5610000000000001</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.599</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.549</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>0.5659999999999999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>0.538</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>0.603</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>0.547</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>0.431</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>0.578</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>0.332</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>0.298</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>0.522</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21">
         <v>0.603</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21">
         <v>0.5649999999999999</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21">
         <v>0.542</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U21">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V21">
         <v>0.493</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W21">
         <v>0.433</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X21">
         <v>0.589</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21">
         <v>0.524</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z21">
         <v>0.476</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA21">
         <v>0.474</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>r_Refinery</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:27">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
         <v>0.746</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.615</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.613</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.556</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.627</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>0.625</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>0.525</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.639</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>0.516</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>0.665</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>0.585</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>0.482</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22">
         <v>0.63</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22">
         <v>0.353</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>0.301</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>0.552</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22">
         <v>0.673</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22">
         <v>0.569</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22">
         <v>0.574</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U22">
         <v>0.493</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V22">
         <v>1</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W22">
         <v>0.476</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X22">
         <v>0.6860000000000001</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22">
         <v>0.54</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z22">
         <v>0.507</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA22">
         <v>0.518</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>r_Sugar_Allied_Industries</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:27">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
         <v>0.651</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.511</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.499</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.477</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.495</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>0.552</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.444</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>0.512</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>0.457</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>0.5620000000000001</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>0.51</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>0.433</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>0.53</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>0.278</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>0.27</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>0.421</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23">
         <v>0.515</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23">
         <v>0.504</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23">
         <v>0.455</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23">
         <v>0.433</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23">
         <v>0.476</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W23">
         <v>1</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X23">
         <v>0.552</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23">
         <v>0.488</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z23">
         <v>0.494</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA23">
         <v>0.456</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>r_Technology_Communication</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:27">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
         <v>0.874</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.713</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.6879999999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.655</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.698</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.749</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>0.614</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>0.743</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>0.607</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>0.784</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>0.707</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>0.5580000000000001</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24">
         <v>0.763</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24">
         <v>0.415</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>0.37</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>0.549</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24">
         <v>0.717</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24">
         <v>0.698</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24">
         <v>0.649</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U24">
         <v>0.589</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V24">
         <v>0.6860000000000001</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W24">
         <v>0.552</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X24">
         <v>1</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y24">
         <v>0.656</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z24">
         <v>0.612</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AA24">
         <v>0.587</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>r_Textile_Composite</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:27">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
         <v>0.782</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.57</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.614</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.5620000000000001</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.647</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>0.656</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>0.546</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>0.663</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>0.546</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>0.676</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>0.631</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>0.489</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>0.638</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>0.363</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25">
         <v>0.316</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>0.478</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25">
         <v>0.614</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25">
         <v>0.646</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T25">
         <v>0.573</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U25">
         <v>0.524</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25">
         <v>0.54</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W25">
         <v>0.488</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X25">
         <v>0.656</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y25">
         <v>1</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z25">
         <v>0.606</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA25">
         <v>0.513</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>r_Textile_Spinning</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:27">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
         <v>0.748</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>0.5580000000000001</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.527</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.539</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.542</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>0.613</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>0.503</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>0.592</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>0.52</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>0.638</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>0.571</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>0.487</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26">
         <v>0.633</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26">
         <v>0.315</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26">
         <v>0.32</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26">
         <v>0.421</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R26">
         <v>0.5620000000000001</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26">
         <v>0.57</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T26">
         <v>0.512</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26">
         <v>0.476</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26">
         <v>0.507</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W26">
         <v>0.494</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X26">
         <v>0.612</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y26">
         <v>0.606</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z26">
         <v>1</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA26">
         <v>0.469</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>r_Transport</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:27">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
         <v>0.678</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>0.546</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.549</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.516</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0.526</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>0.587</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>0.51</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>0.582</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>0.503</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>0.601</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>0.531</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>0.452</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27">
         <v>0.578</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27">
         <v>0.32</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27">
         <v>0.278</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27">
         <v>0.463</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R27">
         <v>0.574</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27">
         <v>0.551</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T27">
         <v>0.528</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U27">
         <v>0.474</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V27">
         <v>0.518</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W27">
         <v>0.456</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X27">
         <v>0.587</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y27">
         <v>0.513</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="Z27">
         <v>0.469</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AA27">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>